--- a/cet4/result/79_侦探女神_真相揭秘的逆袭/79_侦探女神_真相揭秘的逆袭_学习版.xlsx
+++ b/cet4/result/79_侦探女神_真相揭秘的逆袭/79_侦探女神_真相揭秘的逆袭_学习版.xlsx
@@ -397,1025 +397,759 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D53"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>lake</v>
       </c>
       <c r="B2" t="str">
-        <v>lake</v>
+        <v>/leɪk/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D2" t="str">
         <v>湖</v>
       </c>
-      <c r="D2" t="str">
-        <v>lake(湖)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>sad</v>
       </c>
       <c r="B3" t="str">
-        <v>sad</v>
+        <v>/sæd/</v>
       </c>
       <c r="C3" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D3" t="str">
         <v>悲伤</v>
       </c>
-      <c r="D3" t="str">
-        <v>sad(悲伤)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>case</v>
       </c>
       <c r="B4" t="str">
-        <v>case</v>
+        <v>/keɪs/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D4" t="str">
         <v>案件</v>
       </c>
-      <c r="D4" t="str">
-        <v>case(案件)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>wedding</v>
       </c>
       <c r="B5" t="str">
-        <v>wedding</v>
+        <v>/ˈwedɪŋ/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D5" t="str">
         <v>婚礼</v>
       </c>
-      <c r="D5" t="str">
-        <v>wedding(婚礼)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>efficient</v>
       </c>
       <c r="B6" t="str">
-        <v>efficient</v>
+        <v>/ɪˈfɪʃnt/</v>
       </c>
       <c r="C6" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>有效率的</v>
       </c>
-      <c r="D6" t="str">
-        <v>efficient(有效率的)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>specialize</v>
       </c>
       <c r="B7" t="str">
-        <v>specialize</v>
+        <v>/ˈspeʃəlaɪz/</v>
       </c>
       <c r="C7" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D7" t="str">
         <v>专门从事</v>
       </c>
-      <c r="D7" t="str">
-        <v>specialize(专门从事)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>work</v>
       </c>
       <c r="B8" t="str">
-        <v>work</v>
+        <v>/wɜːrk/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D8" t="str">
         <v>工作</v>
       </c>
-      <c r="D8" t="str">
-        <v>work(工作)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>coarse</v>
       </c>
       <c r="B9" t="str">
-        <v>coarse</v>
+        <v>/kɔːrs/</v>
       </c>
       <c r="C9" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>粗糙的</v>
       </c>
-      <c r="D9" t="str">
-        <v>coarse(粗糙的)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>leather</v>
       </c>
       <c r="B10" t="str">
-        <v>leather</v>
+        <v>/ˈleðər/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>皮革</v>
       </c>
-      <c r="D10" t="str">
-        <v>leather(皮革)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>boot</v>
       </c>
       <c r="B11" t="str">
-        <v>boot</v>
+        <v>/buːt/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D11" t="str">
         <v>靴子</v>
       </c>
-      <c r="D11" t="str">
-        <v>boot(靴子)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>track</v>
       </c>
       <c r="B12" t="str">
-        <v>track</v>
+        <v>/træk/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D12" t="str">
         <v>轨迹</v>
       </c>
-      <c r="D12" t="str">
-        <v>track(轨迹)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>dense</v>
       </c>
       <c r="B13" t="str">
-        <v>track</v>
+        <v>/dens/</v>
       </c>
       <c r="C13" t="str">
-        <v>轨道</v>
+        <v>adj.</v>
       </c>
       <c r="D13" t="str">
-        <v>track(轨道)📢</v>
+        <v>稠密的</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>lock</v>
       </c>
       <c r="B14" t="str">
-        <v>dense</v>
+        <v>/lɑːk/</v>
       </c>
       <c r="C14" t="str">
-        <v>稠密的</v>
+        <v>n./v.</v>
       </c>
       <c r="D14" t="str">
-        <v>dense(稠密的)📢</v>
+        <v>锁</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>durable</v>
       </c>
       <c r="B15" t="str">
-        <v>lock</v>
+        <v>/ˈdʊrəbl/</v>
       </c>
       <c r="C15" t="str">
-        <v>锁</v>
+        <v>n./adj.</v>
       </c>
       <c r="D15" t="str">
-        <v>lock(锁)📢</v>
+        <v>耐用的</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>metre</v>
       </c>
       <c r="B16" t="str">
-        <v>durable</v>
+        <v>/ˈmiːtər/</v>
       </c>
       <c r="C16" t="str">
-        <v>耐用的</v>
+        <v>n.</v>
       </c>
       <c r="D16" t="str">
-        <v>durable(耐用的)📢</v>
+        <v>米</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>ticket</v>
       </c>
       <c r="B17" t="str">
-        <v>metre</v>
+        <v>/ˈtɪkɪt/</v>
       </c>
       <c r="C17" t="str">
-        <v>米</v>
+        <v>n./vt.</v>
       </c>
       <c r="D17" t="str">
-        <v>metre(米)📢</v>
+        <v>票</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>Canada</v>
       </c>
       <c r="B18" t="str">
-        <v>ticket</v>
+        <v>/ˈkænədə/</v>
       </c>
       <c r="C18" t="str">
-        <v>票</v>
+        <v>n.</v>
       </c>
       <c r="D18" t="str">
-        <v>ticket(票)📢</v>
+        <v>加拿大</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>doubt</v>
       </c>
       <c r="B19" t="str">
-        <v>Canada</v>
+        <v>/daʊt/</v>
       </c>
       <c r="C19" t="str">
-        <v>加拿大</v>
+        <v>n./v.</v>
       </c>
       <c r="D19" t="str">
-        <v>Canada(加拿大)📢</v>
+        <v>怀疑</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>maybe</v>
       </c>
       <c r="B20" t="str">
-        <v>doubt</v>
+        <v>/ˈmeɪbi/</v>
       </c>
       <c r="C20" t="str">
-        <v>怀疑</v>
+        <v>n./v./adv.</v>
       </c>
       <c r="D20" t="str">
-        <v>doubt(怀疑)📢</v>
+        <v>可能</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>discuss</v>
       </c>
       <c r="B21" t="str">
-        <v>maybe</v>
+        <v>/dɪˈskʌs/</v>
       </c>
       <c r="C21" t="str">
-        <v>可能</v>
+        <v>vt.</v>
       </c>
       <c r="D21" t="str">
-        <v>maybe(可能)📢</v>
+        <v>讨论</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>eighty</v>
       </c>
       <c r="B22" t="str">
-        <v>discuss</v>
+        <v>/ˈeɪti/</v>
       </c>
       <c r="C22" t="str">
-        <v>讨论</v>
+        <v>n./adj./num.</v>
       </c>
       <c r="D22" t="str">
-        <v>discuss(讨论)📢</v>
+        <v>八十</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>dictation</v>
       </c>
       <c r="B23" t="str">
-        <v>eighty</v>
+        <v>/dɪkˈteɪʃn/</v>
       </c>
       <c r="C23" t="str">
-        <v>八十</v>
+        <v>n.</v>
       </c>
       <c r="D23" t="str">
-        <v>eighty(八十)📢</v>
+        <v>听写</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>add</v>
       </c>
       <c r="B24" t="str">
-        <v>dictation</v>
+        <v>/æd/</v>
       </c>
       <c r="C24" t="str">
-        <v>听写</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D24" t="str">
-        <v>dictation(听写)📢</v>
+        <v>添加</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>protest</v>
       </c>
       <c r="B25" t="str">
-        <v>maybe</v>
+        <v>/ˈprəʊtest/</v>
       </c>
       <c r="C25" t="str">
-        <v>可能</v>
+        <v>n./v.</v>
       </c>
       <c r="D25" t="str">
-        <v>maybe(可能)📢</v>
+        <v>抗议</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>frighten</v>
       </c>
       <c r="B26" t="str">
-        <v>add</v>
+        <v>/ˈfraɪtn/</v>
       </c>
       <c r="C26" t="str">
-        <v>添加</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D26" t="str">
-        <v>add(添加)📢</v>
+        <v>害怕</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>atmospheric</v>
       </c>
       <c r="B27" t="str">
-        <v>protest</v>
+        <v>/ˌætməsˈfɪrɪk,ˌætməsˈferɪk/</v>
       </c>
       <c r="C27" t="str">
-        <v>抗议</v>
+        <v>adj.</v>
       </c>
       <c r="D27" t="str">
-        <v>protest(抗议)📢</v>
+        <v>大气的</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>microphone</v>
       </c>
       <c r="B28" t="str">
-        <v>frighten</v>
+        <v>/ˈmaɪkrəfoʊn/</v>
       </c>
       <c r="C28" t="str">
-        <v>害怕</v>
+        <v>n.</v>
       </c>
       <c r="D28" t="str">
-        <v>frighten(害怕)📢</v>
+        <v>麦克风</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>rag</v>
       </c>
       <c r="B29" t="str">
-        <v>atmospheric</v>
+        <v>/ræɡ/</v>
       </c>
       <c r="C29" t="str">
-        <v>大气的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D29" t="str">
-        <v>atmospheric(大气的)📢</v>
+        <v>破布</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>ache</v>
       </c>
       <c r="B30" t="str">
-        <v>microphone</v>
+        <v>/eɪk/</v>
       </c>
       <c r="C30" t="str">
-        <v>麦克风</v>
+        <v>n./vi.</v>
       </c>
       <c r="D30" t="str">
-        <v>microphone(麦克风)📢</v>
+        <v>疼痛</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>reveal</v>
       </c>
       <c r="B31" t="str">
-        <v>rag</v>
+        <v>/rɪˈviːl/</v>
       </c>
       <c r="C31" t="str">
-        <v>破布</v>
+        <v>n./vt.</v>
       </c>
       <c r="D31" t="str">
-        <v>rag(破布)📢</v>
+        <v>揭示</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>refrigerator</v>
       </c>
       <c r="B32" t="str">
-        <v>ache</v>
+        <v>/rɪˈfrɪdʒəreɪtər/</v>
       </c>
       <c r="C32" t="str">
-        <v>疼痛</v>
+        <v>n.</v>
       </c>
       <c r="D32" t="str">
-        <v>ache(疼痛)📢</v>
+        <v>冰箱</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>tend</v>
       </c>
       <c r="B33" t="str">
-        <v>maybe</v>
+        <v>/tend/</v>
       </c>
       <c r="C33" t="str">
-        <v>可能</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D33" t="str">
-        <v>maybe(可能)📢</v>
+        <v>倾向于</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>clearly</v>
       </c>
       <c r="B34" t="str">
-        <v>reveal</v>
+        <v>/ˈklɪrli/</v>
       </c>
       <c r="C34" t="str">
-        <v>揭示</v>
+        <v>v./adv.</v>
       </c>
       <c r="D34" t="str">
-        <v>reveal(揭示)📢</v>
+        <v>清晰地</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>declare</v>
       </c>
       <c r="B35" t="str">
-        <v>eighty</v>
+        <v>/dɪˈkler/</v>
       </c>
       <c r="C35" t="str">
-        <v>八十</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D35" t="str">
-        <v>eighty(八十)📢</v>
+        <v>宣布</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>aid</v>
       </c>
       <c r="B36" t="str">
-        <v>Canada</v>
+        <v>/eɪd/</v>
       </c>
       <c r="C36" t="str">
-        <v>加拿大</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D36" t="str">
-        <v>Canada(加拿大)📢</v>
+        <v>援助</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>thick</v>
       </c>
       <c r="B37" t="str">
-        <v>refrigerator</v>
+        <v>/θɪk/</v>
       </c>
       <c r="C37" t="str">
-        <v>冰箱</v>
+        <v>n./adj.</v>
       </c>
       <c r="D37" t="str">
-        <v>refrigerator(冰箱)📢</v>
+        <v>厚的</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>foot</v>
       </c>
       <c r="B38" t="str">
-        <v>reveal</v>
+        <v>/fʊt/</v>
       </c>
       <c r="C38" t="str">
-        <v>揭露</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D38" t="str">
-        <v>reveal(揭露)📢</v>
+        <v>脚</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>over</v>
       </c>
       <c r="B39" t="str">
-        <v>tend</v>
+        <v>/ˈoʊvər/</v>
       </c>
       <c r="C39" t="str">
-        <v>倾向于</v>
+        <v>n./vt./v./adj./adv./prep.</v>
       </c>
       <c r="D39" t="str">
-        <v>tend(倾向于)📢</v>
+        <v>结束</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>charge</v>
       </c>
       <c r="B40" t="str">
-        <v>clearly</v>
+        <v>/tʃɑːrdʒ/</v>
       </c>
       <c r="C40" t="str">
-        <v>清晰地</v>
+        <v>n./v.</v>
       </c>
       <c r="D40" t="str">
-        <v>clearly(清晰地)📢</v>
+        <v>控诉</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>hope</v>
       </c>
       <c r="B41" t="str">
-        <v>declare</v>
+        <v>/hoʊp/</v>
       </c>
       <c r="C41" t="str">
-        <v>宣布</v>
+        <v>n./v.</v>
       </c>
       <c r="D41" t="str">
-        <v>declare(宣布)📢</v>
+        <v>希望</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>prison</v>
       </c>
       <c r="B42" t="str">
-        <v>track</v>
+        <v>/ˈprɪzn/</v>
       </c>
       <c r="C42" t="str">
-        <v>足迹</v>
+        <v>n./vt.</v>
       </c>
       <c r="D42" t="str">
-        <v>track(足迹)📢</v>
+        <v>监狱</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>imprison</v>
       </c>
       <c r="B43" t="str">
-        <v>aid</v>
+        <v>/ɪmˈprɪzn/</v>
       </c>
       <c r="C43" t="str">
-        <v>援助</v>
+        <v>vt.</v>
       </c>
       <c r="D43" t="str">
-        <v>aid(援助)📢</v>
+        <v>监禁</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>butcher</v>
       </c>
       <c r="B44" t="str">
-        <v>thick</v>
+        <v>/ˈbʊtʃər/</v>
       </c>
       <c r="C44" t="str">
-        <v>厚的</v>
+        <v>n./v.</v>
       </c>
       <c r="D44" t="str">
-        <v>thick(厚的)📢</v>
+        <v>屠夫</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>dragon</v>
       </c>
       <c r="B45" t="str">
-        <v>foot</v>
+        <v>/ˈdræɡən/</v>
       </c>
       <c r="C45" t="str">
-        <v>脚</v>
+        <v>n.</v>
       </c>
       <c r="D45" t="str">
-        <v>foot(脚)📢</v>
+        <v>龙</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>enlarge</v>
       </c>
       <c r="B46" t="str">
-        <v>over</v>
+        <v>/ɪnˈlɑːrdʒ/</v>
       </c>
       <c r="C46" t="str">
-        <v>结束</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D46" t="str">
-        <v>over(结束)📢</v>
+        <v>扩大</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>comfort</v>
       </c>
       <c r="B47" t="str">
-        <v>charge</v>
+        <v>/ˈkʌmfərt/</v>
       </c>
       <c r="C47" t="str">
-        <v>控诉</v>
+        <v>n./vt.</v>
       </c>
       <c r="D47" t="str">
-        <v>charge(控诉)📢</v>
+        <v>安慰</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>blast</v>
       </c>
       <c r="B48" t="str">
-        <v>protest</v>
+        <v>/blæst/</v>
       </c>
       <c r="C48" t="str">
-        <v>反抗</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D48" t="str">
-        <v>protest(反抗)📢</v>
+        <v>爆炸</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>leak</v>
       </c>
       <c r="B49" t="str">
-        <v>hope</v>
+        <v>/liːk/</v>
       </c>
       <c r="C49" t="str">
-        <v>希望</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D49" t="str">
-        <v>hope(希望)📢</v>
+        <v>泄漏</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>outskirt</v>
       </c>
       <c r="B50" t="str">
-        <v>reveal</v>
+        <v>/'aʊt,skɜːrt/</v>
       </c>
       <c r="C50" t="str">
-        <v>揭示</v>
+        <v>n.</v>
       </c>
       <c r="D50" t="str">
-        <v>reveal(揭示)📢</v>
+        <v>郊区</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>row</v>
       </c>
       <c r="B51" t="str">
-        <v>eighty</v>
+        <v>/roʊ; raʊ/</v>
       </c>
       <c r="C51" t="str">
-        <v>八十</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D51" t="str">
-        <v>eighty(八十)📢</v>
+        <v>排</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>51</v>
+      <c r="A52" t="str">
+        <v>hedge</v>
       </c>
       <c r="B52" t="str">
-        <v>prison</v>
+        <v>/hedʒ/</v>
       </c>
       <c r="C52" t="str">
-        <v>监狱</v>
+        <v>n./v.</v>
       </c>
       <c r="D52" t="str">
-        <v>prison(监狱)📢</v>
+        <v>树篱</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53">
-        <v>52</v>
+      <c r="A53" t="str">
+        <v>worth</v>
       </c>
       <c r="B53" t="str">
-        <v>imprison</v>
+        <v>/wɜːrθ/</v>
       </c>
       <c r="C53" t="str">
-        <v>监禁</v>
+        <v>n./adj.</v>
       </c>
       <c r="D53" t="str">
-        <v>imprison(监禁)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>butcher</v>
-      </c>
-      <c r="C54" t="str">
-        <v>屠夫</v>
-      </c>
-      <c r="D54" t="str">
-        <v>butcher(屠夫)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>dragon</v>
-      </c>
-      <c r="C55" t="str">
-        <v>龙</v>
-      </c>
-      <c r="D55" t="str">
-        <v>dragon(龙)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>Canada</v>
-      </c>
-      <c r="C56" t="str">
-        <v>加拿大</v>
-      </c>
-      <c r="D56" t="str">
-        <v>Canada(加拿大)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>enlarge</v>
-      </c>
-      <c r="C57" t="str">
-        <v>扩大</v>
-      </c>
-      <c r="D57" t="str">
-        <v>enlarge(扩大)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>comfort</v>
-      </c>
-      <c r="C58" t="str">
-        <v>安慰</v>
-      </c>
-      <c r="D58" t="str">
-        <v>comfort(安慰)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>work</v>
-      </c>
-      <c r="C59" t="str">
-        <v>工作</v>
-      </c>
-      <c r="D59" t="str">
-        <v>work(工作)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>blast</v>
-      </c>
-      <c r="C60" t="str">
-        <v>爆炸</v>
-      </c>
-      <c r="D60" t="str">
-        <v>blast(爆炸)📢</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
-        <v>efficient</v>
-      </c>
-      <c r="C61" t="str">
-        <v>高效的</v>
-      </c>
-      <c r="D61" t="str">
-        <v>efficient(高效的)📢</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="str">
-        <v>leak</v>
-      </c>
-      <c r="C62" t="str">
-        <v>泄漏</v>
-      </c>
-      <c r="D62" t="str">
-        <v>leak(泄漏)📢</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="str">
-        <v>eighty</v>
-      </c>
-      <c r="C63" t="str">
-        <v>八十</v>
-      </c>
-      <c r="D63" t="str">
-        <v>eighty(八十)📢</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="str">
-        <v>outskirt</v>
-      </c>
-      <c r="C64" t="str">
-        <v>郊区</v>
-      </c>
-      <c r="D64" t="str">
-        <v>outskirt(郊区)📢</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="str">
-        <v>row</v>
-      </c>
-      <c r="C65" t="str">
-        <v>排</v>
-      </c>
-      <c r="D65" t="str">
-        <v>row(排)📢</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="str">
-        <v>hedge</v>
-      </c>
-      <c r="C66" t="str">
-        <v>树篱</v>
-      </c>
-      <c r="D66" t="str">
-        <v>hedge(树篱)📢</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" t="str">
-        <v>case</v>
-      </c>
-      <c r="C67" t="str">
-        <v>案件</v>
-      </c>
-      <c r="D67" t="str">
-        <v>case(案件)📢</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" t="str">
-        <v>sad</v>
-      </c>
-      <c r="C68" t="str">
-        <v>悲伤的</v>
-      </c>
-      <c r="D68" t="str">
-        <v>sad(悲伤的)📢</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69">
-        <v>68</v>
-      </c>
-      <c r="B69" t="str">
-        <v>worth</v>
-      </c>
-      <c r="C69" t="str">
         <v>价值</v>
-      </c>
-      <c r="D69" t="str">
-        <v>worth(价值)📢</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70">
-        <v>69</v>
-      </c>
-      <c r="B70" t="str">
-        <v>hope</v>
-      </c>
-      <c r="C70" t="str">
-        <v>希望</v>
-      </c>
-      <c r="D70" t="str">
-        <v>hope(希望)📢</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71">
-        <v>70</v>
-      </c>
-      <c r="B71" t="str">
-        <v>eighty</v>
-      </c>
-      <c r="C71" t="str">
-        <v>八十</v>
-      </c>
-      <c r="D71" t="str">
-        <v>eighty(八十)📢</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72">
-        <v>71</v>
-      </c>
-      <c r="B72" t="str">
-        <v>lake</v>
-      </c>
-      <c r="C72" t="str">
-        <v>湖</v>
-      </c>
-      <c r="D72" t="str">
-        <v>lake(湖)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D72"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D53"/>
   </ignoredErrors>
 </worksheet>
 </file>